--- a/artfynd/A 7957-2022 artfynd.xlsx
+++ b/artfynd/A 7957-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7957-2022 artfynd.xlsx
+++ b/artfynd/A 7957-2022 artfynd.xlsx
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112025066</v>
+        <v>112025186</v>
       </c>
       <c r="B2" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817105</v>
+        <v>817340</v>
       </c>
       <c r="R2" t="n">
-        <v>7524965</v>
+        <v>7524915</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112025138</v>
+        <v>112025177</v>
       </c>
       <c r="B3" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,31 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817335</v>
+        <v>817340</v>
       </c>
       <c r="R3" t="n">
-        <v>7524930</v>
+        <v>7524915</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,17 +860,13 @@
           <t>2023-08-31</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>födosök i tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112025177</v>
+        <v>112026024</v>
       </c>
       <c r="B4" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>817340</v>
+        <v>816880</v>
       </c>
       <c r="R4" t="n">
-        <v>7524915</v>
+        <v>7525050</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112025056</v>
+        <v>112026008</v>
       </c>
       <c r="B5" t="n">
-        <v>90815</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>817061</v>
+        <v>816910</v>
       </c>
       <c r="R5" t="n">
-        <v>7524945</v>
+        <v>7525035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,37 +1095,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112026008</v>
+        <v>112026113</v>
       </c>
       <c r="B6" t="n">
-        <v>81386</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>816911</v>
+        <v>816864</v>
       </c>
       <c r="R6" t="n">
-        <v>7525035</v>
+        <v>7525180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112025110</v>
+        <v>112025834</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>817135</v>
+        <v>816955</v>
       </c>
       <c r="R7" t="n">
-        <v>7524960</v>
+        <v>7525000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,37 +1305,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112025093</v>
+        <v>112025069</v>
       </c>
       <c r="B8" t="n">
-        <v>88181</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>817131</v>
+        <v>817105</v>
       </c>
       <c r="R8" t="n">
-        <v>7524960</v>
+        <v>7524965</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,15 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112025452</v>
+        <v>112025110</v>
       </c>
       <c r="B9" t="n">
-        <v>90858</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>817251</v>
+        <v>817135</v>
       </c>
       <c r="R9" t="n">
-        <v>7524790</v>
+        <v>7524960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,15 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112025485</v>
+        <v>112025471</v>
       </c>
       <c r="B10" t="n">
-        <v>90449</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1607,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>817135</v>
+        <v>817250</v>
       </c>
       <c r="R10" t="n">
-        <v>7524971</v>
+        <v>7524790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,12 +1587,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,15 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112026024</v>
+        <v>112025056</v>
       </c>
       <c r="B11" t="n">
-        <v>89554</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,21 +1631,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1717,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>816880</v>
+        <v>817060</v>
       </c>
       <c r="R11" t="n">
-        <v>7525050</v>
+        <v>7524945</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,15 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112025186</v>
+        <v>112025485</v>
       </c>
       <c r="B12" t="n">
-        <v>77732</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1796,27 +1736,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>4745</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1827,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>817340</v>
+        <v>817135</v>
       </c>
       <c r="R12" t="n">
-        <v>7524915</v>
+        <v>7524970</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,12 +1797,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1890,15 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112025069</v>
+        <v>112025452</v>
       </c>
       <c r="B13" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>817105</v>
+        <v>817250</v>
       </c>
       <c r="R13" t="n">
-        <v>7524965</v>
+        <v>7524790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,37 +1935,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112025834</v>
+        <v>112025066</v>
       </c>
       <c r="B14" t="n">
-        <v>90801</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2047,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>816955</v>
+        <v>817105</v>
       </c>
       <c r="R14" t="n">
-        <v>7525000</v>
+        <v>7524965</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2110,51 +2040,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112025210</v>
+        <v>112025093</v>
       </c>
       <c r="B15" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2162,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>817315</v>
+        <v>817130</v>
       </c>
       <c r="R15" t="n">
-        <v>7524815</v>
+        <v>7524960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2200,17 +2120,13 @@
           <t>2023-08-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>födosök i tall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2229,15 +2145,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112025521</v>
+        <v>112025138</v>
       </c>
       <c r="B16" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2178,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2277,7 +2188,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>817085</v>
+        <v>817335</v>
       </c>
       <c r="R16" t="n">
         <v>7524930</v>
@@ -2307,17 +2218,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack i tall</t>
+          <t>födosök i tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2344,15 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112025471</v>
+        <v>112025210</v>
       </c>
       <c r="B17" t="n">
-        <v>90809</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,30 +2266,35 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2391,10 +2302,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>817251</v>
+        <v>817315</v>
       </c>
       <c r="R17" t="n">
-        <v>7524790</v>
+        <v>7524815</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2429,13 +2340,17 @@
           <t>2023-08-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>födosök i tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2454,15 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112026113</v>
+        <v>112025521</v>
       </c>
       <c r="B18" t="n">
-        <v>90831</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,30 +2380,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2501,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>816864</v>
+        <v>817085</v>
       </c>
       <c r="R18" t="n">
-        <v>7525180</v>
+        <v>7524930</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2531,12 +2442,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack i tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2545,7 +2461,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7957-2022 artfynd.xlsx
+++ b/artfynd/A 7957-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025186</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025177</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026008</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026113</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025069</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025110</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025471</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025056</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025485</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025452</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025066</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025093</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2252,6 +2327,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025138</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025210</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,8 +2561,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112025521</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>